--- a/Tango/TuVung2/3week5day/tuvung.xlsx
+++ b/Tango/TuVung2/3week5day/tuvung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\01_LearningJapaneseWebProject\Tango\TuVung2\3week5day\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7627C057-749C-4811-A6F4-07044FB8EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C779B7-CD5E-4EF4-94F0-4DF08473DCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
   <si>
     <t>japanese</t>
   </si>
@@ -39,262 +39,286 @@
     <t>subjapanese</t>
   </si>
   <si>
-    <t>第3週の5日目</t>
-  </si>
-  <si>
-    <t>宴会を開く</t>
-  </si>
-  <si>
-    <t>えんかいをひらく</t>
-  </si>
-  <si>
-    <t>mở tiệc</t>
-  </si>
-  <si>
-    <t>飲み会</t>
-  </si>
-  <si>
-    <t>のみかい</t>
-  </si>
-  <si>
-    <t>tiệc nhậu</t>
-  </si>
-  <si>
-    <t>そうべつかい</t>
-  </si>
-  <si>
-    <t>送別会</t>
-  </si>
-  <si>
-    <t>tiệc chia tay</t>
-  </si>
-  <si>
-    <t>かんげいかい</t>
-  </si>
-  <si>
-    <t>歓迎会</t>
-  </si>
-  <si>
-    <t>tiệc chào mừng</t>
-  </si>
-  <si>
-    <t>飲み放題</t>
-  </si>
-  <si>
-    <t>のみほうだい</t>
-  </si>
-  <si>
-    <t>食べ放題</t>
-  </si>
-  <si>
-    <t>たべほうだい</t>
-  </si>
-  <si>
-    <t>ăn thoả thích</t>
-  </si>
-  <si>
-    <t>uống thoả thích</t>
-  </si>
-  <si>
-    <t>お酒を注ぐ</t>
-  </si>
-  <si>
-    <t>おさけをつぐ</t>
-  </si>
-  <si>
-    <t>rót rượu vào ly</t>
-  </si>
-  <si>
-    <t>おゆをそそぐ</t>
-  </si>
-  <si>
-    <t>お湯を注ぐ</t>
-  </si>
-  <si>
-    <t>ró nước nóng</t>
-  </si>
-  <si>
-    <t>かんぱいする</t>
-  </si>
-  <si>
-    <t>乾杯する</t>
-  </si>
-  <si>
-    <t>cạn ly</t>
-  </si>
-  <si>
-    <t>盛り上がる</t>
-  </si>
-  <si>
-    <t>もりあがる</t>
-  </si>
-  <si>
-    <t>nổi hứng lên</t>
-  </si>
-  <si>
-    <t>つちがもりあがる</t>
-  </si>
-  <si>
-    <t>土が盛り上がる</t>
-  </si>
-  <si>
-    <t>đất bằng dậy sóng</t>
-  </si>
-  <si>
-    <t>ビールの泡</t>
-  </si>
-  <si>
-    <t>ビールのあわ</t>
-  </si>
-  <si>
-    <t>bọt chia</t>
-  </si>
-  <si>
-    <t>あふれる</t>
-  </si>
-  <si>
-    <t>tràn ly</t>
-  </si>
-  <si>
-    <t>こぼす</t>
-  </si>
-  <si>
-    <t>làm đổ</t>
-  </si>
-  <si>
-    <t>こぼれる</t>
-  </si>
-  <si>
-    <t>bị đổ</t>
-  </si>
-  <si>
-    <t>ビールを一気に飲む</t>
-  </si>
-  <si>
-    <t>ビールをいっきにのむ</t>
-  </si>
-  <si>
-    <t>uống bia một hơi</t>
-  </si>
-  <si>
-    <t>お酒をよう</t>
-  </si>
-  <si>
-    <t>say rượu</t>
-  </si>
-  <si>
-    <t>よっぱらう</t>
-  </si>
-  <si>
-    <t>say mèm</t>
-  </si>
-  <si>
-    <t>よっぱらい</t>
-  </si>
-  <si>
-    <t>người say rượu</t>
-  </si>
-  <si>
-    <t>あばれる</t>
-  </si>
-  <si>
-    <t>quậy phá</t>
-  </si>
-  <si>
-    <t>にぎやか</t>
-  </si>
-  <si>
-    <t>náo nhiệt</t>
-  </si>
-  <si>
-    <t>やかましい</t>
-  </si>
-  <si>
-    <t>huyên náo</t>
-  </si>
-  <si>
-    <t>さわがしい</t>
-  </si>
-  <si>
-    <t>ồn ào, ầm ĩ</t>
-  </si>
-  <si>
-    <t>そうぞうしい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ồn ào </t>
-  </si>
-  <si>
-    <t>たばこの煙</t>
-  </si>
-  <si>
     <t>たばこおけむり</t>
   </si>
   <si>
-    <t>たばこのけむり</t>
-  </si>
-  <si>
-    <t>khói thuốc lá</t>
-  </si>
-  <si>
-    <t>煙い/煙たい</t>
-  </si>
-  <si>
-    <t>けむい/けむたい</t>
-  </si>
-  <si>
-    <t>đầy khói</t>
-  </si>
-  <si>
-    <t>割る</t>
-  </si>
-  <si>
-    <t>làm vỡ</t>
-  </si>
-  <si>
-    <t>をわる</t>
-  </si>
-  <si>
-    <t>割れる</t>
-  </si>
-  <si>
-    <t>がわれる</t>
-  </si>
-  <si>
-    <t>bị vỡ</t>
-  </si>
-  <si>
-    <t>倒す</t>
-  </si>
-  <si>
-    <t>をたおす</t>
-  </si>
-  <si>
-    <t>làm đổ, ngã</t>
-  </si>
-  <si>
-    <t>倒れる</t>
-  </si>
-  <si>
-    <t>がたおれる</t>
-  </si>
-  <si>
-    <t>ほかの客に迷惑をかける</t>
-  </si>
-  <si>
-    <t>ほかのきゃくにめいわくをかける</t>
-  </si>
-  <si>
-    <t>làm phiền đến khách khác</t>
-  </si>
-  <si>
-    <t>迷惑がかかる</t>
-  </si>
-  <si>
-    <t>めいわくがかかる</t>
-  </si>
-  <si>
-    <t>gầy phiền cho người khác</t>
+    <t>長男</t>
+  </si>
+  <si>
+    <t>ちょうなん</t>
+  </si>
+  <si>
+    <t>trưởng nam</t>
+  </si>
+  <si>
+    <t>長女</t>
+  </si>
+  <si>
+    <t>ちょうじょ</t>
+  </si>
+  <si>
+    <t>trưởng nữ</t>
+  </si>
+  <si>
+    <t>次男</t>
+  </si>
+  <si>
+    <t>じなん</t>
+  </si>
+  <si>
+    <t>thứ nam</t>
+  </si>
+  <si>
+    <t>三男</t>
+  </si>
+  <si>
+    <t>さんなん</t>
+  </si>
+  <si>
+    <t>3 con trai</t>
+  </si>
+  <si>
+    <t>末っ子</t>
+  </si>
+  <si>
+    <t>すえっこ</t>
+  </si>
+  <si>
+    <t>con út</t>
+  </si>
+  <si>
+    <t>叔父</t>
+  </si>
+  <si>
+    <t>おじ</t>
+  </si>
+  <si>
+    <t>bác trai, cậu, chú,...</t>
+  </si>
+  <si>
+    <t>叔母</t>
+  </si>
+  <si>
+    <t>おば</t>
+  </si>
+  <si>
+    <t>bác gái, dì, cô,...</t>
+  </si>
+  <si>
+    <t>職場</t>
+  </si>
+  <si>
+    <t>しょくば</t>
+  </si>
+  <si>
+    <t>nơi làm việc</t>
+  </si>
+  <si>
+    <t>同僚</t>
+  </si>
+  <si>
+    <t>どうりょう</t>
+  </si>
+  <si>
+    <t>đồng nghiệp</t>
+  </si>
+  <si>
+    <t>上司</t>
+  </si>
+  <si>
+    <t>じょうし</t>
+  </si>
+  <si>
+    <t>cấp trên</t>
+  </si>
+  <si>
+    <t>部下</t>
+  </si>
+  <si>
+    <t>ぶか</t>
+  </si>
+  <si>
+    <t>cấp dưới</t>
+  </si>
+  <si>
+    <t>先輩</t>
+  </si>
+  <si>
+    <t>せんぱい</t>
+  </si>
+  <si>
+    <t>tiền bối</t>
+  </si>
+  <si>
+    <t>後輩</t>
+  </si>
+  <si>
+    <t>こうはい</t>
+  </si>
+  <si>
+    <t>hậu bối</t>
+  </si>
+  <si>
+    <t>部長</t>
+  </si>
+  <si>
+    <t>ぶちょう</t>
+  </si>
+  <si>
+    <t>trưởng phòng</t>
+  </si>
+  <si>
+    <t>課長</t>
+  </si>
+  <si>
+    <t>かちょう</t>
+  </si>
+  <si>
+    <t>trưởng bộ phận</t>
+  </si>
+  <si>
+    <t>大学生</t>
+  </si>
+  <si>
+    <t>だいがくせい</t>
+  </si>
+  <si>
+    <t>sinh viên đại học</t>
+  </si>
+  <si>
+    <t>高校生</t>
+  </si>
+  <si>
+    <t>こうこうせい</t>
+  </si>
+  <si>
+    <t>học sinh cấp 3</t>
+  </si>
+  <si>
+    <t>中学生</t>
+  </si>
+  <si>
+    <t>ちゅうがくせい</t>
+  </si>
+  <si>
+    <t>học sinh cấp 2</t>
+  </si>
+  <si>
+    <t>サラリーマン</t>
+  </si>
+  <si>
+    <t>người làm thuê</t>
+  </si>
+  <si>
+    <t>主婦</t>
+  </si>
+  <si>
+    <t>しゅふ</t>
+  </si>
+  <si>
+    <t>bà nội trợ</t>
+  </si>
+  <si>
+    <t>～人兄弟</t>
+  </si>
+  <si>
+    <t>～にんきょうだい</t>
+  </si>
+  <si>
+    <t>～anh em</t>
+  </si>
+  <si>
+    <t>関係</t>
+  </si>
+  <si>
+    <t>かんけい</t>
+  </si>
+  <si>
+    <t>mối quan hệ</t>
+  </si>
+  <si>
+    <t>～姉妹</t>
+  </si>
+  <si>
+    <t>しまい</t>
+  </si>
+  <si>
+    <t>～chị em gái</t>
+  </si>
+  <si>
+    <t>親類</t>
+  </si>
+  <si>
+    <t>しんるい</t>
+  </si>
+  <si>
+    <t>người thân</t>
+  </si>
+  <si>
+    <t>親戚</t>
+  </si>
+  <si>
+    <t>しんせき</t>
+  </si>
+  <si>
+    <t>họ hàng</t>
+  </si>
+  <si>
+    <t>甥</t>
+  </si>
+  <si>
+    <t>おい</t>
+  </si>
+  <si>
+    <t>cháu trai (gọi bác...)</t>
+  </si>
+  <si>
+    <t>姪</t>
+  </si>
+  <si>
+    <t>めい</t>
+  </si>
+  <si>
+    <t>cháu gái (gọi bác...)</t>
+  </si>
+  <si>
+    <t>従兄弟</t>
+  </si>
+  <si>
+    <t>いとこ</t>
+  </si>
+  <si>
+    <t>anh em họ</t>
+  </si>
+  <si>
+    <t>一人っ子</t>
+  </si>
+  <si>
+    <t>ひとりっこ</t>
+  </si>
+  <si>
+    <t>con 1</t>
+  </si>
+  <si>
+    <t>一人息子</t>
+  </si>
+  <si>
+    <t>ひとりむすこ</t>
+  </si>
+  <si>
+    <t>1 con trai</t>
+  </si>
+  <si>
+    <t>一人娘</t>
+  </si>
+  <si>
+    <t>ひとりむすめ</t>
+  </si>
+  <si>
+    <t>1 con gái</t>
+  </si>
+  <si>
+    <t>第5週の1日目</t>
   </si>
 </sst>
 </file>
@@ -374,12 +398,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -701,7 +720,7 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>5</v>
@@ -726,10 +745,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>13</v>
@@ -737,16 +756,16 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -757,18 +776,18 @@
         <v>18</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -784,10 +803,10 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -795,10 +814,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>31</v>
@@ -815,12 +834,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>37</v>
@@ -841,199 +860,213 @@
       <c r="B14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="D14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="D15" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="D16" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="D18" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="D20" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="D21" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="D22" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="D23" s="6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="D24" s="6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="D25" s="6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="6"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
@@ -1084,13 +1117,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B5 B11:B12 B19:B21 B23:B24 B26:B33 B42:B51 B14:B15 C26">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:C45">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
